--- a/data/trans_orig/P15A-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P15A-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha tenido un accidente en los últimos tres meses que le ha causado heridas o lesiones suficientes para limitar su actividad normal y/o para necesitar asistencia sanitaria en 2007</t>
+          <t>Población que ha tenido un accidente en los últimos tres meses que le ha causado heridas o lesiones suficientes para limitar su actividad normal y/o para necesitar asistencia sanitaria en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>14646</t>
+          <t>14203</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>34081</t>
+          <t>34820</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>9647</t>
+          <t>9210</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>25733</t>
+          <t>24952</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>28013</t>
+          <t>27199</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>53308</t>
+          <t>50664</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,66%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>659931</t>
+          <t>659192</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>679366</t>
+          <t>679809</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,09%</t>
+          <t>94,98%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>97,95%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>662618</t>
+          <t>663399</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>678704</t>
+          <t>679141</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,26%</t>
+          <t>96,38%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,66%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1329055</t>
+          <t>1331699</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1354350</t>
+          <t>1355164</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,14%</t>
+          <t>96,34%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>98,03%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>30944</t>
+          <t>30068</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>57041</t>
+          <t>57193</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>20213</t>
+          <t>20460</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>43206</t>
+          <t>42737</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>54950</t>
+          <t>57130</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>91354</t>
+          <t>91522</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,74%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>904759</t>
+          <t>904607</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>930856</t>
+          <t>931732</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,07%</t>
+          <t>94,05%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,78%</t>
+          <t>96,87%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>925187</t>
+          <t>925656</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>948180</t>
+          <t>947933</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,54%</t>
+          <t>95,59%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,91%</t>
+          <t>97,89%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1838839</t>
+          <t>1838671</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1875243</t>
+          <t>1873063</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,27%</t>
+          <t>95,26%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,15%</t>
+          <t>97,04%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>15752</t>
+          <t>15404</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>36220</t>
+          <t>35548</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>15164</t>
+          <t>15904</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>35416</t>
+          <t>35199</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>35328</t>
+          <t>35861</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>63457</t>
+          <t>62853</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,61%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>642289</t>
+          <t>642961</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>662757</t>
+          <t>663105</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,66%</t>
+          <t>94,76%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>97,73%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>648425</t>
+          <t>648642</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>668677</t>
+          <t>667937</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,82%</t>
+          <t>94,85%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>97,67%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1298893</t>
+          <t>1299497</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1327022</t>
+          <t>1326489</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,34%</t>
+          <t>95,39%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>97,37%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>24117</t>
+          <t>23433</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>46814</t>
+          <t>45739</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>15135</t>
+          <t>14560</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>35691</t>
+          <t>35443</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>42691</t>
+          <t>43535</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>73266</t>
+          <t>73203</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>895408</t>
+          <t>896483</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>918105</t>
+          <t>918789</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,03%</t>
+          <t>95,15%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>97,51%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1002921</t>
+          <t>1003169</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1023477</t>
+          <t>1024052</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,56%</t>
+          <t>96,59%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,6%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1907568</t>
+          <t>1907631</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1938143</t>
+          <t>1937299</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1965,7 +1965,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>97,8%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>102111</t>
+          <t>103130</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>144855</t>
+          <t>147090</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>75288</t>
+          <t>75267</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>115059</t>
+          <t>116065</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>189848</t>
+          <t>190759</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>251213</t>
+          <t>249424</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,75%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3131688</t>
+          <t>3129453</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3174432</t>
+          <t>3173413</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,58%</t>
+          <t>95,51%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>96,85%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3264138</t>
+          <t>3263132</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3303909</t>
+          <t>3303930</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,7 +2268,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,6%</t>
+          <t>96,57%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6404528</t>
+          <t>6406317</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6465893</t>
+          <t>6464982</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,23%</t>
+          <t>96,25%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,15%</t>
+          <t>97,13%</t>
         </is>
       </c>
     </row>
@@ -2485,7 +2485,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha tenido un accidente en los últimos tres meses que le ha causado heridas o lesiones suficientes para limitar su actividad normal y/o para necesitar asistencia sanitaria en 2012</t>
+          <t>Población que ha tenido un accidente en los últimos tres meses que le ha causado heridas o lesiones suficientes para limitar su actividad normal y/o para necesitar asistencia sanitaria en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8388</t>
+          <t>8007</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>23747</t>
+          <t>22060</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>14938</t>
+          <t>16023</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>36904</t>
+          <t>38351</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>26830</t>
+          <t>27062</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>51762</t>
+          <t>52036</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,72%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>679722</t>
+          <t>681409</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>695081</t>
+          <t>695462</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,62%</t>
+          <t>96,86%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,86%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>660146</t>
+          <t>658699</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>682112</t>
+          <t>681027</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,71%</t>
+          <t>94,5%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,86%</t>
+          <t>97,7%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1348757</t>
+          <t>1348483</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1373689</t>
+          <t>1373457</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,3%</t>
+          <t>96,28%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>98,07%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>20461</t>
+          <t>20206</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>43932</t>
+          <t>44767</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>19062</t>
+          <t>19453</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>40334</t>
+          <t>42113</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>44320</t>
+          <t>43611</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>76096</t>
+          <t>74677</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,64%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>974015</t>
+          <t>973180</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>997486</t>
+          <t>997741</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,68%</t>
+          <t>95,6%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>98,02%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>991850</t>
+          <t>990071</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1013122</t>
+          <t>1012731</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,09%</t>
+          <t>95,92%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,15%</t>
+          <t>98,12%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1974035</t>
+          <t>1975454</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2005811</t>
+          <t>2006520</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,29%</t>
+          <t>96,36%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>97,87%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>11892</t>
+          <t>11837</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>31111</t>
+          <t>30755</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>13639</t>
+          <t>13128</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>32295</t>
+          <t>32330</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,7 +3416,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>28833</t>
+          <t>29206</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>56550</t>
+          <t>56108</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,66%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>726512</t>
+          <t>726868</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>745731</t>
+          <t>745786</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,89%</t>
+          <t>95,94%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>98,44%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>744879</t>
+          <t>744844</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>763535</t>
+          <t>764046</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3534,7 +3534,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>98,31%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1478247</t>
+          <t>1478689</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1505964</t>
+          <t>1505591</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,32%</t>
+          <t>96,34%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>98,1%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>23418</t>
+          <t>23950</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>47260</t>
+          <t>47909</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>14808</t>
+          <t>16040</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>36401</t>
+          <t>36014</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>43365</t>
+          <t>44121</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>74965</t>
+          <t>75939</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,8%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>900479</t>
+          <t>899830</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>924321</t>
+          <t>923789</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,01%</t>
+          <t>94,94%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,53%</t>
+          <t>97,47%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1015500</t>
+          <t>1015887</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1037093</t>
+          <t>1035861</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,54%</t>
+          <t>96,58%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>98,48%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1924675</t>
+          <t>1923701</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1956275</t>
+          <t>1955519</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,25%</t>
+          <t>96,2%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>97,79%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>80016</t>
+          <t>80175</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>122151</t>
+          <t>120595</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4072,7 +4072,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>79889</t>
+          <t>78736</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>120306</t>
+          <t>119152</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>167014</t>
+          <t>169870</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>226559</t>
+          <t>228695</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,27%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3304628</t>
+          <t>3306184</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3346763</t>
+          <t>3346604</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,7 +4180,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,44%</t>
+          <t>96,48%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3438003</t>
+          <t>3439157</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3478420</t>
+          <t>3479573</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,62%</t>
+          <t>96,65%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>97,79%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6758529</t>
+          <t>6756393</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6818074</t>
+          <t>6815218</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,76%</t>
+          <t>96,73%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,61%</t>
+          <t>97,57%</t>
         </is>
       </c>
     </row>
@@ -4432,7 +4432,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha tenido un accidente en los últimos tres meses que le ha causado heridas o lesiones suficientes para limitar su actividad normal y/o para necesitar asistencia sanitaria en 2016</t>
+          <t>Población que ha tenido un accidente en los últimos tres meses que le ha causado heridas o lesiones suficientes para limitar su actividad normal y/o para necesitar asistencia sanitaria en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9591</t>
+          <t>9639</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>25324</t>
+          <t>25751</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>11469</t>
+          <t>11082</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>29021</t>
+          <t>28287</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>24090</t>
+          <t>25237</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>46167</t>
+          <t>48396</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,59%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>649476</t>
+          <t>649049</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>665209</t>
+          <t>665161</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,25%</t>
+          <t>96,18%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,57%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>643818</t>
+          <t>644552</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>661370</t>
+          <t>661757</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,69%</t>
+          <t>95,8%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>98,35%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1301472</t>
+          <t>1299243</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1323549</t>
+          <t>1322402</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,57%</t>
+          <t>96,41%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,13%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>22507</t>
+          <t>22238</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>46221</t>
+          <t>45199</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>14595</t>
+          <t>15115</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>36918</t>
+          <t>37087</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>43431</t>
+          <t>41963</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>74249</t>
+          <t>73522</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,56%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>976210</t>
+          <t>977232</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>999924</t>
+          <t>1000193</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,48%</t>
+          <t>95,58%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>97,83%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1005995</t>
+          <t>1005826</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1028318</t>
+          <t>1027798</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,46%</t>
+          <t>96,44%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,55%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1991095</t>
+          <t>1991822</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2021913</t>
+          <t>2023381</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,41%</t>
+          <t>96,44%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>97,97%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6413</t>
+          <t>6161</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>20301</t>
+          <t>20530</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5332</t>
+          <t>5451</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>18773</t>
+          <t>19065</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>14649</t>
+          <t>15125</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>35457</t>
+          <t>34592</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,24%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>739251</t>
+          <t>739022</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>753139</t>
+          <t>753391</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,33%</t>
+          <t>97,3%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,19%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>766238</t>
+          <t>765946</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>779679</t>
+          <t>779560</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,61%</t>
+          <t>97,57%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,31%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1509106</t>
+          <t>1509971</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1529914</t>
+          <t>1529438</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>97,76%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>99,02%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>18487</t>
+          <t>18131</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>38612</t>
+          <t>39811</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>23984</t>
+          <t>22710</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>48634</t>
+          <t>49891</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>47491</t>
+          <t>47332</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>80737</t>
+          <t>80220</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,05%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>898955</t>
+          <t>897756</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>919080</t>
+          <t>919436</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,88%</t>
+          <t>95,75%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,03%</t>
+          <t>98,07%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>995145</t>
+          <t>993888</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1019795</t>
+          <t>1021069</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,34%</t>
+          <t>95,22%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>97,82%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1900609</t>
+          <t>1901126</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1933855</t>
+          <t>1934014</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,93%</t>
+          <t>95,95%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>97,61%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>72684</t>
+          <t>71065</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>108185</t>
+          <t>108483</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>71030</t>
+          <t>69056</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>110136</t>
+          <t>107560</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>150790</t>
+          <t>152738</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>205997</t>
+          <t>206076</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,7 +6084,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3286165</t>
+          <t>3285867</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3321666</t>
+          <t>3323285</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,81%</t>
+          <t>96,8%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,86%</t>
+          <t>97,91%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3434406</t>
+          <t>3436982</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3473512</t>
+          <t>3475486</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
+          <t>96,97%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,0%</t>
+          <t>98,05%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6732895</t>
+          <t>6732816</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6788102</t>
+          <t>6786154</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6202,7 +6202,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>97,8%</t>
         </is>
       </c>
     </row>
@@ -6379,7 +6379,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha tenido un accidente en los últimos tres meses que le ha causado heridas o lesiones suficientes para limitar su actividad normal y/o para necesitar asistencia sanitaria en 2023</t>
+          <t>Población que ha tenido un accidente en los últimos tres meses que le ha causado heridas o lesiones suficientes para limitar su actividad normal y/o para necesitar asistencia sanitaria en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6574,12 +6574,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9705</t>
+          <t>9094</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>32846</t>
+          <t>30904</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6609,12 +6609,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>14190</t>
+          <t>14014</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>26427</t>
+          <t>26550</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>26877</t>
+          <t>26889</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>51207</t>
+          <t>51237</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6687,12 +6687,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>602595</t>
+          <t>604537</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>625736</t>
+          <t>626347</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,83%</t>
+          <t>95,14%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,57%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6722,12 +6722,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>649325</t>
+          <t>649202</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>661562</t>
+          <t>661738</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,09%</t>
+          <t>96,07%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>97,93%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6757,12 +6757,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1259987</t>
+          <t>1259957</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1284317</t>
+          <t>1284305</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6917,12 +6917,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12388</t>
+          <t>13071</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>41790</t>
+          <t>42297</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>18920</t>
+          <t>18182</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>41418</t>
+          <t>39975</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>35567</t>
+          <t>35898</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>73777</t>
+          <t>75748</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,52%</t>
         </is>
       </c>
     </row>
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1151074</t>
+          <t>1150567</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1180476</t>
+          <t>1179793</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,5%</t>
+          <t>96,45%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,96%</t>
+          <t>98,9%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>916688</t>
+          <t>918131</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>939186</t>
+          <t>939924</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,68%</t>
+          <t>95,83%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,03%</t>
+          <t>98,1%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2077194</t>
+          <t>2075223</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2115404</t>
+          <t>2115073</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,57%</t>
+          <t>96,48%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,33%</t>
         </is>
       </c>
     </row>
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6249</t>
+          <t>5829</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>20994</t>
+          <t>20468</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>10569</t>
+          <t>9339</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>31570</t>
+          <t>31264</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>19785</t>
+          <t>20235</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>44824</t>
+          <t>44823</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,7 +7345,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -7373,12 +7373,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>683686</t>
+          <t>684212</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>698431</t>
+          <t>698851</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,02%</t>
+          <t>97,1%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,17%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>901796</t>
+          <t>902102</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>922797</t>
+          <t>924027</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,62%</t>
+          <t>96,65%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>99,0%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1593222</t>
+          <t>1593223</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1618261</t>
+          <t>1617811</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7463,7 +7463,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>98,76%</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10679</t>
+          <t>10854</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>27611</t>
+          <t>27748</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>17469</t>
+          <t>16638</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>33908</t>
+          <t>33569</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>31674</t>
+          <t>31342</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>53788</t>
+          <t>53542</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,65%</t>
         </is>
       </c>
     </row>
@@ -7716,12 +7716,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>899220</t>
+          <t>899083</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>916152</t>
+          <t>915977</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,02%</t>
+          <t>97,01%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>98,83%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1061024</t>
+          <t>1061363</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1077463</t>
+          <t>1078294</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>96,93%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>98,48%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1967975</t>
+          <t>1968221</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1990089</t>
+          <t>1990421</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,34%</t>
+          <t>97,35%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>98,45%</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>54522</t>
+          <t>52714</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>97424</t>
+          <t>97446</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,7 +7961,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>73012</t>
+          <t>71915</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>114774</t>
+          <t>111038</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>134783</t>
+          <t>133759</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>193208</t>
+          <t>191295</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,69%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3362393</t>
+          <t>3362371</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3405295</t>
+          <t>3407103</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8079,7 +8079,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>98,48%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3547383</t>
+          <t>3551119</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3589145</t>
+          <t>3590242</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,87%</t>
+          <t>96,97%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,01%</t>
+          <t>98,04%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6928766</t>
+          <t>6930679</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6987191</t>
+          <t>6988215</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>97,31%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,12%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P15A-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P15A-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>14203</t>
+          <t>14230</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>34820</t>
+          <t>33460</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>9210</t>
+          <t>8944</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>24952</t>
+          <t>24731</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>27199</t>
+          <t>28188</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>50664</t>
+          <t>51478</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,72%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>659192</t>
+          <t>660552</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>679809</t>
+          <t>679782</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,98%</t>
+          <t>95,18%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>663399</t>
+          <t>663620</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>679141</t>
+          <t>679407</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,38%</t>
+          <t>96,41%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,7%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1331699</t>
+          <t>1330885</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1355164</t>
+          <t>1354175</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,34%</t>
+          <t>96,28%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,03%</t>
+          <t>97,96%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>30068</t>
+          <t>30991</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>57193</t>
+          <t>57770</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>20460</t>
+          <t>20376</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>42737</t>
+          <t>42237</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>57130</t>
+          <t>57169</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>91522</t>
+          <t>91152</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,72%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>904607</t>
+          <t>904030</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>931732</t>
+          <t>930809</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,05%</t>
+          <t>93,99%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,87%</t>
+          <t>96,78%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>925656</t>
+          <t>926156</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>947933</t>
+          <t>948017</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,59%</t>
+          <t>95,64%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>97,9%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1838671</t>
+          <t>1839041</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1873063</t>
+          <t>1873024</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,26%</t>
+          <t>95,28%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>15404</t>
+          <t>15170</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>35548</t>
+          <t>35820</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>15904</t>
+          <t>15860</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>35199</t>
+          <t>35415</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>35861</t>
+          <t>35334</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>62853</t>
+          <t>63876</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,69%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>642961</t>
+          <t>642689</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>663105</t>
+          <t>663339</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,76%</t>
+          <t>94,72%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,73%</t>
+          <t>97,76%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>648642</t>
+          <t>648426</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>667937</t>
+          <t>667981</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,85%</t>
+          <t>94,82%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>97,68%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1299497</t>
+          <t>1298474</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1326489</t>
+          <t>1327016</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,39%</t>
+          <t>95,31%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,37%</t>
+          <t>97,41%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>23433</t>
+          <t>23333</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>45739</t>
+          <t>47233</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>14560</t>
+          <t>14979</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>35443</t>
+          <t>34794</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>43535</t>
+          <t>43780</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>73203</t>
+          <t>76801</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,88%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>896483</t>
+          <t>894989</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>918789</t>
+          <t>918889</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,15%</t>
+          <t>94,99%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,51%</t>
+          <t>97,52%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1003169</t>
+          <t>1003818</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1024052</t>
+          <t>1023633</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,59%</t>
+          <t>96,65%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,56%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1907631</t>
+          <t>1904033</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1937299</t>
+          <t>1937054</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,3%</t>
+          <t>96,12%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>97,79%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>103130</t>
+          <t>102848</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>147090</t>
+          <t>146963</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,7 +2120,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>75267</t>
+          <t>75895</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>116065</t>
+          <t>113942</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>190759</t>
+          <t>190398</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>249424</t>
+          <t>247827</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,72%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3129453</t>
+          <t>3129580</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3173413</t>
+          <t>3173695</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2238,7 +2238,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,85%</t>
+          <t>96,86%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3263132</t>
+          <t>3265255</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3303930</t>
+          <t>3303302</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,57%</t>
+          <t>96,63%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>97,75%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6406317</t>
+          <t>6407914</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6464982</t>
+          <t>6465343</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,25%</t>
+          <t>96,28%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,13%</t>
+          <t>97,14%</t>
         </is>
       </c>
     </row>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8007</t>
+          <t>7535</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>22060</t>
+          <t>22463</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>16023</t>
+          <t>15552</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>38351</t>
+          <t>36300</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>27062</t>
+          <t>28071</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>52036</t>
+          <t>52434</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,74%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>681409</t>
+          <t>681006</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>695462</t>
+          <t>695934</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,86%</t>
+          <t>96,81%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,86%</t>
+          <t>98,93%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>658699</t>
+          <t>660750</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>681027</t>
+          <t>681498</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,5%</t>
+          <t>94,79%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>97,77%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1348483</t>
+          <t>1348085</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1373457</t>
+          <t>1372448</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,28%</t>
+          <t>96,26%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,07%</t>
+          <t>98,0%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>20206</t>
+          <t>19117</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>44767</t>
+          <t>42627</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>19453</t>
+          <t>18411</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>42113</t>
+          <t>39704</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>43611</t>
+          <t>44453</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>74677</t>
+          <t>76397</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,73%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>973180</t>
+          <t>975320</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>997741</t>
+          <t>998830</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,6%</t>
+          <t>95,81%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>98,12%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>990071</t>
+          <t>992480</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1012731</t>
+          <t>1013773</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,92%</t>
+          <t>96,15%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>98,22%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1975454</t>
+          <t>1973734</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2006520</t>
+          <t>2005678</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,36%</t>
+          <t>96,27%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,87%</t>
+          <t>97,83%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>11837</t>
+          <t>12546</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>30755</t>
+          <t>30266</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>13128</t>
+          <t>13009</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>32330</t>
+          <t>31959</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>29206</t>
+          <t>29449</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>56108</t>
+          <t>56973</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,71%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>726868</t>
+          <t>727357</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>745786</t>
+          <t>745077</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,94%</t>
+          <t>96,01%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>98,34%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>744844</t>
+          <t>745215</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>764046</t>
+          <t>764165</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,84%</t>
+          <t>95,89%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,33%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1478689</t>
+          <t>1477824</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1505591</t>
+          <t>1505348</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,34%</t>
+          <t>96,29%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,1%</t>
+          <t>98,08%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>23950</t>
+          <t>23723</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>47909</t>
+          <t>47175</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>16040</t>
+          <t>15979</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>36014</t>
+          <t>35828</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3764,7 +3764,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>44121</t>
+          <t>44547</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>75939</t>
+          <t>74505</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,73%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>899830</t>
+          <t>900564</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>923789</t>
+          <t>924016</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,94%</t>
+          <t>95,02%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,5%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1015887</t>
+          <t>1016073</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1035861</t>
+          <t>1035922</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,7 +3872,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,58%</t>
+          <t>96,59%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1923701</t>
+          <t>1925135</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1955519</t>
+          <t>1955093</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,2%</t>
+          <t>96,27%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,79%</t>
+          <t>97,77%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>80175</t>
+          <t>78985</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>120595</t>
+          <t>119930</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>78736</t>
+          <t>80274</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>119152</t>
+          <t>120256</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>169870</t>
+          <t>168303</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>228695</t>
+          <t>227313</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,25%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3306184</t>
+          <t>3306849</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3346604</t>
+          <t>3347794</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,48%</t>
+          <t>96,5%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>97,7%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3439157</t>
+          <t>3438053</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3479573</t>
+          <t>3478035</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,65%</t>
+          <t>96,62%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,79%</t>
+          <t>97,74%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6756393</t>
+          <t>6757775</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6815218</t>
+          <t>6816785</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,73%</t>
+          <t>96,75%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>97,59%</t>
         </is>
       </c>
     </row>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9639</t>
+          <t>9604</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>25751</t>
+          <t>24860</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>11082</t>
+          <t>11454</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>28287</t>
+          <t>29703</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>25237</t>
+          <t>24889</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>48396</t>
+          <t>47640</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,54%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>649049</t>
+          <t>649940</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>665161</t>
+          <t>665196</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,18%</t>
+          <t>96,32%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,57%</t>
+          <t>98,58%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>644552</t>
+          <t>643136</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>661757</t>
+          <t>661385</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,8%</t>
+          <t>95,59%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,3%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1299243</t>
+          <t>1299999</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1322402</t>
+          <t>1322750</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,41%</t>
+          <t>96,46%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,13%</t>
+          <t>98,15%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>22238</t>
+          <t>23292</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>45199</t>
+          <t>47555</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>15115</t>
+          <t>14399</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>37087</t>
+          <t>36382</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>41963</t>
+          <t>42659</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>73522</t>
+          <t>74838</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,62%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>977232</t>
+          <t>974876</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1000193</t>
+          <t>999139</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,58%</t>
+          <t>95,35%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>97,72%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1005826</t>
+          <t>1006531</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1027798</t>
+          <t>1028514</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,44%</t>
+          <t>96,51%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,55%</t>
+          <t>98,62%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1991822</t>
+          <t>1990506</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2023381</t>
+          <t>2022685</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,44%</t>
+          <t>96,38%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>97,93%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6161</t>
+          <t>6933</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>20530</t>
+          <t>20862</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5451</t>
+          <t>5184</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>19065</t>
+          <t>18906</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>15125</t>
+          <t>15298</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>34592</t>
+          <t>34168</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,21%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>739022</t>
+          <t>738690</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>753391</t>
+          <t>752619</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>97,25%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>99,09%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>765946</t>
+          <t>766105</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>779560</t>
+          <t>779827</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>97,59%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,34%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1509971</t>
+          <t>1510395</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1529438</t>
+          <t>1529265</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>97,79%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>99,01%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>18131</t>
+          <t>18327</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>39811</t>
+          <t>39420</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>22710</t>
+          <t>24025</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>49891</t>
+          <t>48443</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>47332</t>
+          <t>47560</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>80220</t>
+          <t>79324</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,0%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>897756</t>
+          <t>898147</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>919436</t>
+          <t>919240</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,75%</t>
+          <t>95,8%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,07%</t>
+          <t>98,05%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>993888</t>
+          <t>995336</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1021069</t>
+          <t>1019754</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,22%</t>
+          <t>95,36%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>97,7%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1901126</t>
+          <t>1902022</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1934014</t>
+          <t>1933786</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,95%</t>
+          <t>96,0%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,61%</t>
+          <t>97,6%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>71065</t>
+          <t>70895</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>108483</t>
+          <t>108804</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6019,7 +6019,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>69056</t>
+          <t>69712</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>107560</t>
+          <t>110150</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>152738</t>
+          <t>152632</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>206076</t>
+          <t>205724</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6089,7 +6089,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,96%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3285867</t>
+          <t>3285546</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3323285</t>
+          <t>3323455</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,7 +6127,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,8%</t>
+          <t>96,79%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3436982</t>
+          <t>3434392</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3475486</t>
+          <t>3474830</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,97%</t>
+          <t>96,89%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>98,03%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6732816</t>
+          <t>6733168</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6786154</t>
+          <t>6786260</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,7 +6197,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,03%</t>
+          <t>97,04%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -6569,32 +6569,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>16586</t>
+          <t>18863</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9094</t>
+          <t>10101</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>30904</t>
+          <t>34845</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6604,32 +6604,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>19143</t>
+          <t>20358</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>14014</t>
+          <t>14230</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>26550</t>
+          <t>27756</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>35729</t>
+          <t>39221</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>26889</t>
+          <t>29270</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>51237</t>
+          <t>56469</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,97%</t>
         </is>
       </c>
     </row>
@@ -6682,32 +6682,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>618855</t>
+          <t>671847</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>604537</t>
+          <t>655865</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>626347</t>
+          <t>680609</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>97,39%</t>
+          <t>97,27%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,14%</t>
+          <t>94,96%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,57%</t>
+          <t>98,54%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6717,32 +6717,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>656609</t>
+          <t>712755</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>649202</t>
+          <t>705357</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>661738</t>
+          <t>718883</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>97,17%</t>
+          <t>97,22%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,07%</t>
+          <t>96,21%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,93%</t>
+          <t>98,06%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6752,32 +6752,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1275465</t>
+          <t>1384602</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1259957</t>
+          <t>1367354</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1284305</t>
+          <t>1394553</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>97,25%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,09%</t>
+          <t>96,03%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,95%</t>
+          <t>97,94%</t>
         </is>
       </c>
     </row>
@@ -6795,17 +6795,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6830,17 +6830,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>675752</t>
+          <t>733113</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>675752</t>
+          <t>733113</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>675752</t>
+          <t>733113</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1311194</t>
+          <t>1423823</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1311194</t>
+          <t>1423823</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1311194</t>
+          <t>1423823</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6912,32 +6912,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>26822</t>
+          <t>30790</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13071</t>
+          <t>20488</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>42297</t>
+          <t>46683</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6947,32 +6947,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>27542</t>
+          <t>30368</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>18182</t>
+          <t>20790</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>39975</t>
+          <t>45271</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>54364</t>
+          <t>61158</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>35898</t>
+          <t>45816</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>75748</t>
+          <t>80750</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,81%</t>
         </is>
       </c>
     </row>
@@ -7025,32 +7025,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1166042</t>
+          <t>1018127</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1150567</t>
+          <t>1002234</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1179793</t>
+          <t>1028429</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>97,06%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,45%</t>
+          <t>95,55%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,9%</t>
+          <t>98,05%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7060,32 +7060,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>930564</t>
+          <t>1040470</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>918131</t>
+          <t>1025567</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>939924</t>
+          <t>1050048</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>97,13%</t>
+          <t>97,16%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,83%</t>
+          <t>95,77%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,1%</t>
+          <t>98,06%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>2096607</t>
+          <t>2058597</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2075223</t>
+          <t>2039005</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2115073</t>
+          <t>2073939</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,11%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,48%</t>
+          <t>96,19%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,33%</t>
+          <t>97,84%</t>
         </is>
       </c>
     </row>
@@ -7138,17 +7138,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7173,17 +7173,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>958106</t>
+          <t>1070838</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>958106</t>
+          <t>1070838</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>958106</t>
+          <t>1070838</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>2150971</t>
+          <t>2119755</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2150971</t>
+          <t>2119755</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2150971</t>
+          <t>2119755</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7255,32 +7255,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>12016</t>
+          <t>15161</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5829</t>
+          <t>8544</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>20468</t>
+          <t>26787</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7290,32 +7290,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>20650</t>
+          <t>22430</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9339</t>
+          <t>16399</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>31264</t>
+          <t>32016</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>32665</t>
+          <t>37591</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>20235</t>
+          <t>27319</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>44823</t>
+          <t>49683</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>3,08%</t>
         </is>
       </c>
     </row>
@@ -7368,32 +7368,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>692664</t>
+          <t>787912</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>684212</t>
+          <t>776286</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>698851</t>
+          <t>794529</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>98,11%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,1%</t>
+          <t>96,66%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>98,94%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7403,32 +7403,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>912716</t>
+          <t>789829</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>902102</t>
+          <t>780243</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>924027</t>
+          <t>795860</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>97,79%</t>
+          <t>97,24%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,65%</t>
+          <t>96,06%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,0%</t>
+          <t>97,98%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1605381</t>
+          <t>1577741</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1593223</t>
+          <t>1565649</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1617811</t>
+          <t>1588013</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>98,01%</t>
+          <t>97,67%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,26%</t>
+          <t>96,92%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,31%</t>
         </is>
       </c>
     </row>
@@ -7481,17 +7481,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7516,17 +7516,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7598,32 +7598,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>17506</t>
+          <t>17528</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10854</t>
+          <t>10416</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>27748</t>
+          <t>26868</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7633,32 +7633,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>24151</t>
+          <t>26283</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>16638</t>
+          <t>18504</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>33569</t>
+          <t>35431</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,22 +7668,22 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>41657</t>
+          <t>43811</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>31342</t>
+          <t>32732</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>53542</t>
+          <t>56345</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
@@ -7693,7 +7693,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,67%</t>
         </is>
       </c>
     </row>
@@ -7711,32 +7711,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>909325</t>
+          <t>972534</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>899083</t>
+          <t>963194</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>915977</t>
+          <t>979646</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,23%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>97,29%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>98,95%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7746,32 +7746,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>1070781</t>
+          <t>1092758</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1061363</t>
+          <t>1083610</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1078294</t>
+          <t>1100537</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>97,79%</t>
+          <t>97,65%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,93%</t>
+          <t>96,83%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>98,35%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,27 +7781,27 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1980106</t>
+          <t>2065293</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1968221</t>
+          <t>2052759</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1990421</t>
+          <t>2076372</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>97,94%</t>
+          <t>97,92%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,35%</t>
+          <t>97,33%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -7824,17 +7824,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7859,17 +7859,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1094932</t>
+          <t>1119041</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1094932</t>
+          <t>1119041</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1094932</t>
+          <t>1119041</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2021763</t>
+          <t>2109104</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2021763</t>
+          <t>2109104</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2021763</t>
+          <t>2109104</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7941,32 +7941,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>72930</t>
+          <t>82343</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>52714</t>
+          <t>65126</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>97446</t>
+          <t>107011</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7976,67 +7976,67 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>91486</t>
+          <t>99438</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>71915</t>
+          <t>82827</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>111038</t>
+          <t>119612</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
+          <t>2,66%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>2,22%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>3,2%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>237</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>181781</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>156515</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>211970</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
           <t>2,5%</t>
         </is>
       </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>1,96%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>3,03%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>237</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>164416</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>133759</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>191295</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>2,31%</t>
-        </is>
-      </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,92%</t>
         </is>
       </c>
     </row>
@@ -8054,32 +8054,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3386887</t>
+          <t>3450419</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3362371</t>
+          <t>3425751</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3407103</t>
+          <t>3467636</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>97,67%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,18%</t>
+          <t>96,97%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>98,16%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8089,67 +8089,67 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3570671</t>
+          <t>3635813</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3551119</t>
+          <t>3615639</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3590242</t>
+          <t>3652424</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
+          <t>97,34%</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>96,8%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>97,78%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>8503</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>7086232</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>7056043</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>7111498</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
           <t>97,5%</t>
         </is>
       </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>96,97%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>98,04%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>8503</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>6957558</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>6930679</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>6988215</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>97,69%</t>
-        </is>
-      </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>97,08%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>97,85%</t>
         </is>
       </c>
     </row>
@@ -8167,17 +8167,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8202,17 +8202,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3662157</t>
+          <t>3735251</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3662157</t>
+          <t>3735251</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3662157</t>
+          <t>3735251</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>7121974</t>
+          <t>7268013</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>7121974</t>
+          <t>7268013</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>7121974</t>
+          <t>7268013</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
